--- a/entertainment_forms/007_tv_series_release_viewer_feedback_form--entertainment_forms.xlsx
+++ b/entertainment_forms/007_tv_series_release_viewer_feedback_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,8 +976,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'action'}</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Action'}</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'comedy'}</t>
+          <t>comedy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Comedy'}</t>
+          <t>Comedy</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'horror'}</t>
+          <t>horror</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Horror'}</t>
+          <t>Horror</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'thriller'}</t>
+          <t>thriller</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Thriller'}</t>
+          <t>Thriller</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'action'}</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Action'}</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'comedy'}</t>
+          <t>comedy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Comedy'}</t>
+          <t>Comedy</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'horror'}</t>
+          <t>horror</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Horror'}</t>
+          <t>Horror</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sci-fi'}</t>
+          <t>sci-fi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sci-Fi'}</t>
+          <t>Sci-Fi</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'thriller'}</t>
+          <t>thriller</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Thriller'}</t>
+          <t>Thriller</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'jenny'}</t>
+          <t>jenny</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'jenny'}</t>
+          <t>jenny</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'review'}</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Review'}</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
